--- a/20250519_SA_ternary/output/system_analysis/system_analysis_main.xlsx
+++ b/20250519_SA_ternary/output/system_analysis/system_analysis_main.xlsx
@@ -40,70 +40,70 @@
     <t>Variance</t>
   </si>
   <si>
+    <t>Er3Co1.87In4</t>
+  </si>
+  <si>
+    <t>Er14Co2In3</t>
+  </si>
+  <si>
+    <t>Er14Co3In3</t>
+  </si>
+  <si>
+    <t>ErCoIn5</t>
+  </si>
+  <si>
+    <t>Er11Co4In9</t>
+  </si>
+  <si>
+    <t>ErCo2.68In0.32</t>
+  </si>
+  <si>
+    <t>Er2CoIn8</t>
+  </si>
+  <si>
     <t>Er6Co2.19In0.81</t>
   </si>
   <si>
-    <t>Er3Co1.87In4</t>
-  </si>
-  <si>
-    <t>Er14Co3In3</t>
-  </si>
-  <si>
-    <t>ErCo2.68In0.32</t>
-  </si>
-  <si>
-    <t>ErCoIn5</t>
+    <t>Er10Co9In20</t>
+  </si>
+  <si>
+    <t>ErCo4In</t>
   </si>
   <si>
     <t>Er8CoIn3</t>
   </si>
   <si>
-    <t>Er11Co4In9</t>
-  </si>
-  <si>
-    <t>Er2CoIn8</t>
-  </si>
-  <si>
-    <t>ErCo4In</t>
-  </si>
-  <si>
-    <t>Er10Co9In20</t>
-  </si>
-  <si>
-    <t>Er14Co2In3</t>
+    <t>Lu3Co2In4</t>
+  </si>
+  <si>
+    <t>Lu14Co2In3</t>
+  </si>
+  <si>
+    <t>Gd14Co3In2.7</t>
+  </si>
+  <si>
+    <t>HoCoGa5</t>
+  </si>
+  <si>
+    <t>Nd11Pd4In9</t>
+  </si>
+  <si>
+    <t>PuNi3</t>
+  </si>
+  <si>
+    <t>Ho2CoGa8</t>
   </si>
   <si>
     <t>Ho6Co2Ga</t>
   </si>
   <si>
-    <t>Lu3Co2In4</t>
-  </si>
-  <si>
-    <t>Gd14Co3In2.7</t>
-  </si>
-  <si>
-    <t>PuNi3</t>
-  </si>
-  <si>
-    <t>HoCoGa5</t>
+    <t>Ho10Ni9In20</t>
+  </si>
+  <si>
+    <t>MgCu4Sn</t>
   </si>
   <si>
     <t>Pr8CoGa3</t>
-  </si>
-  <si>
-    <t>Nd11Pd4In9</t>
-  </si>
-  <si>
-    <t>Ho2CoGa8</t>
-  </si>
-  <si>
-    <t>MgCu4Sn</t>
-  </si>
-  <si>
-    <t>Ho10Ni9In20</t>
-  </si>
-  <si>
-    <t>Lu14Co2In3</t>
   </si>
   <si>
     <t>Er-Er</t>
@@ -539,19 +539,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>2.834</v>
+        <v>2.804</v>
       </c>
       <c r="G3">
-        <v>0.11</v>
+        <v>0.008</v>
       </c>
       <c r="H3">
-        <v>0.012</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -559,19 +559,19 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>2.297</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>0.093</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>0.008999999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -579,16 +579,16 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>2.696</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -599,16 +599,16 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>2.948</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -619,19 +619,19 @@
         <v>35</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>3.124</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>0.228</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>0.052</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -665,19 +665,19 @@
         <v>31</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10">
-        <v>2.804</v>
+        <v>2.72</v>
       </c>
       <c r="G10">
-        <v>0.008</v>
+        <v>0.068</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -708,13 +708,13 @@
         <v>1</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12">
-        <v>2.696</v>
+        <v>2.975</v>
       </c>
       <c r="G12">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -728,13 +728,13 @@
         <v>1</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13">
-        <v>2.948</v>
+        <v>2.999</v>
       </c>
       <c r="G13">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -745,19 +745,19 @@
         <v>35</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>3.203</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -917,16 +917,16 @@
         <v>31</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>2.864</v>
+        <v>0</v>
       </c>
       <c r="G24">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -937,16 +937,16 @@
         <v>32</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>2.471</v>
+        <v>0</v>
       </c>
       <c r="G25">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -957,19 +957,19 @@
         <v>33</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26">
         <v>2</v>
       </c>
       <c r="F26">
-        <v>2.471</v>
+        <v>2.569</v>
       </c>
       <c r="G26">
-        <v>0.016</v>
+        <v>0.173</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -977,16 +977,16 @@
         <v>34</v>
       </c>
       <c r="D27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F27">
-        <v>2.471</v>
+        <v>3.199</v>
       </c>
       <c r="G27">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -997,19 +997,19 @@
         <v>35</v>
       </c>
       <c r="D28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28">
         <v>2</v>
       </c>
       <c r="F28">
-        <v>2.864</v>
+        <v>3.079</v>
       </c>
       <c r="G28">
-        <v>0.007</v>
+        <v>0.17</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1043,19 +1043,19 @@
         <v>31</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>2.831</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>0.081</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1083,19 +1083,19 @@
         <v>33</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F33">
-        <v>2.569</v>
+        <v>2.984</v>
       </c>
       <c r="G33">
-        <v>0.173</v>
+        <v>0.14</v>
       </c>
       <c r="H33">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1103,19 +1103,19 @@
         <v>34</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34">
-        <v>3.199</v>
+        <v>2.947</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>0.029</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1123,19 +1123,19 @@
         <v>35</v>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F35">
-        <v>3.079</v>
+        <v>3.179</v>
       </c>
       <c r="G35">
-        <v>0.17</v>
+        <v>0.031</v>
       </c>
       <c r="H35">
-        <v>0.029</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1169,19 +1169,19 @@
         <v>31</v>
       </c>
       <c r="D38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E38">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F38">
-        <v>2.807</v>
+        <v>2.864</v>
       </c>
       <c r="G38">
-        <v>0.066</v>
+        <v>0.007</v>
       </c>
       <c r="H38">
-        <v>0.004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1189,16 +1189,16 @@
         <v>32</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>2.471</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="H39">
         <v>0</v>
@@ -1209,16 +1209,16 @@
         <v>33</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>2.471</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -1229,16 +1229,16 @@
         <v>34</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>2.471</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="H41">
         <v>0</v>
@@ -1252,16 +1252,16 @@
         <v>2</v>
       </c>
       <c r="E42">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F42">
-        <v>3.179</v>
+        <v>2.864</v>
       </c>
       <c r="G42">
-        <v>0.202</v>
+        <v>0.007</v>
       </c>
       <c r="H42">
-        <v>0.041</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1295,19 +1295,19 @@
         <v>31</v>
       </c>
       <c r="D45">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E45">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F45">
-        <v>2.831</v>
+        <v>0</v>
       </c>
       <c r="G45">
-        <v>0.081</v>
+        <v>0</v>
       </c>
       <c r="H45">
-        <v>0.007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -1335,19 +1335,19 @@
         <v>33</v>
       </c>
       <c r="D47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E47">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F47">
-        <v>2.984</v>
+        <v>2.687</v>
       </c>
       <c r="G47">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="H47">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -1355,19 +1355,19 @@
         <v>34</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E48">
         <v>2</v>
       </c>
       <c r="F48">
-        <v>2.947</v>
+        <v>3.157</v>
       </c>
       <c r="G48">
-        <v>0.029</v>
+        <v>0.095</v>
       </c>
       <c r="H48">
-        <v>0.001</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -1375,19 +1375,19 @@
         <v>35</v>
       </c>
       <c r="D49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E49">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F49">
-        <v>3.179</v>
+        <v>3.222</v>
       </c>
       <c r="G49">
-        <v>0.031</v>
+        <v>0</v>
       </c>
       <c r="H49">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -1421,19 +1421,19 @@
         <v>31</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>2.834</v>
       </c>
       <c r="G52">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -1441,19 +1441,19 @@
         <v>32</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F53">
-        <v>0</v>
+        <v>2.297</v>
       </c>
       <c r="G53">
-        <v>0</v>
+        <v>0.093</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -1461,13 +1461,13 @@
         <v>33</v>
       </c>
       <c r="D54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F54">
-        <v>2.687</v>
+        <v>0</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -1481,19 +1481,19 @@
         <v>34</v>
       </c>
       <c r="D55">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E55">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F55">
-        <v>3.157</v>
+        <v>0</v>
       </c>
       <c r="G55">
-        <v>0.095</v>
+        <v>0</v>
       </c>
       <c r="H55">
-        <v>0.008999999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -1501,19 +1501,19 @@
         <v>35</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56">
-        <v>3.222</v>
+        <v>3.124</v>
       </c>
       <c r="G56">
-        <v>0</v>
+        <v>0.228</v>
       </c>
       <c r="H56">
-        <v>0</v>
+        <v>0.052</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -1547,19 +1547,19 @@
         <v>31</v>
       </c>
       <c r="D59">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E59">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F59">
-        <v>2.922</v>
+        <v>2.962</v>
       </c>
       <c r="G59">
-        <v>0</v>
+        <v>0.052</v>
       </c>
       <c r="H59">
-        <v>0</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -1567,13 +1567,13 @@
         <v>32</v>
       </c>
       <c r="D60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F60">
-        <v>2.492</v>
+        <v>0</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -1587,19 +1587,19 @@
         <v>33</v>
       </c>
       <c r="D61">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E61">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F61">
-        <v>2.922</v>
+        <v>2.685</v>
       </c>
       <c r="G61">
-        <v>0</v>
+        <v>0.035</v>
       </c>
       <c r="H61">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -1673,19 +1673,19 @@
         <v>31</v>
       </c>
       <c r="D66">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E66">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F66">
-        <v>2.962</v>
+        <v>2.922</v>
       </c>
       <c r="G66">
-        <v>0.052</v>
+        <v>0</v>
       </c>
       <c r="H66">
-        <v>0.003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -1693,13 +1693,13 @@
         <v>32</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67">
-        <v>0</v>
+        <v>2.492</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -1713,19 +1713,19 @@
         <v>33</v>
       </c>
       <c r="D68">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E68">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F68">
-        <v>2.685</v>
+        <v>2.922</v>
       </c>
       <c r="G68">
-        <v>0.035</v>
+        <v>0</v>
       </c>
       <c r="H68">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -1802,16 +1802,16 @@
         <v>3</v>
       </c>
       <c r="E73">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F73">
-        <v>2.72</v>
+        <v>2.807</v>
       </c>
       <c r="G73">
-        <v>0.068</v>
+        <v>0.066</v>
       </c>
       <c r="H73">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -1839,13 +1839,13 @@
         <v>33</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F75">
-        <v>2.975</v>
+        <v>0</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -1859,13 +1859,13 @@
         <v>34</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F76">
-        <v>2.999</v>
+        <v>0</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -1879,19 +1879,19 @@
         <v>35</v>
       </c>
       <c r="D77">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E77">
         <v>4</v>
       </c>
       <c r="F77">
-        <v>3.203</v>
+        <v>3.179</v>
       </c>
       <c r="G77">
-        <v>0.111</v>
+        <v>0.202</v>
       </c>
       <c r="H77">
-        <v>0.012</v>
+        <v>0.041</v>
       </c>
     </row>
   </sheetData>
